--- a/Tracker.xlsx
+++ b/Tracker.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29400" windowHeight="12300"/>
+    <workbookView windowWidth="17760" windowHeight="15460"/>
   </bookViews>
   <sheets>
     <sheet name="Tracker" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="967" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="968" uniqueCount="161">
   <si>
     <t>Product Name</t>
   </si>
@@ -330,30 +330,10 @@
     <t>Japan</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>1. https://bitcash.jp/docs/index — homepage. Capture three sections: a) Top banner carousel (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="冬青黑体简体中文"/>
-        <charset val="134"/>
-      </rPr>
-      <t>キャンペーン</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> / campaign banners) — list each campaign title and click for details if needed</t>
-    </r>
+    <t>homepage. Capture three sections: a) Top banner carousel (キャンペーン / campaign banners) — list each campaign title and click for details if needed</t>
+  </si>
+  <si>
+    <t>1. https://bitcash.jp/docs/index</t>
   </si>
   <si>
     <t xml:space="preserve"> https://bitcash.jp/docs/campaign/index</t>
@@ -378,6 +358,9 @@
   </si>
   <si>
     <t>Ovo Cash Gift Card</t>
+  </si>
+  <si>
+    <t>https://www.thejakartapost.com/tag/ovo</t>
   </si>
   <si>
     <t>Bleach Online</t>
@@ -648,7 +631,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -827,11 +810,6 @@
     <font>
       <sz val="10"/>
       <name val="宋体-简"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="冬青黑体简体中文"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -2586,7 +2564,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" ht="61" spans="1:15">
+    <row r="22" ht="17" spans="1:15">
       <c r="A22" s="12" t="s">
         <v>66</v>
       </c>
@@ -2597,15 +2575,17 @@
         <v>68</v>
       </c>
       <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
+      <c r="E22" s="8" t="s">
+        <v>69</v>
+      </c>
       <c r="F22" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I22" s="10" t="s">
         <v>19</v>
@@ -2631,7 +2611,7 @@
     </row>
     <row r="23" spans="1:15">
       <c r="A23" s="12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>32</v>
@@ -2642,7 +2622,7 @@
       <c r="D23" s="8"/>
       <c r="E23" s="7"/>
       <c r="F23" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G23" s="7" t="s">
         <v>19</v>
@@ -2674,18 +2654,18 @@
     </row>
     <row r="24" spans="1:15">
       <c r="A24" s="12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>32</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D24" s="8"/>
       <c r="E24" s="7"/>
       <c r="F24" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G24" s="7" t="s">
         <v>19</v>
@@ -2717,7 +2697,7 @@
     </row>
     <row r="25" spans="1:15">
       <c r="A25" s="12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>67</v>
@@ -2728,7 +2708,7 @@
       <c r="D25" s="8"/>
       <c r="E25" s="7"/>
       <c r="F25" s="7" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
       <c r="G25" s="7" t="s">
         <v>19</v>
@@ -2760,7 +2740,7 @@
     </row>
     <row r="26" spans="1:15">
       <c r="A26" s="12" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>37</v>
@@ -2771,7 +2751,7 @@
       <c r="D26" s="8"/>
       <c r="E26" s="7"/>
       <c r="F26" s="7" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G26" s="7" t="s">
         <v>19</v>
@@ -2803,7 +2783,7 @@
     </row>
     <row r="27" s="1" customFormat="1" spans="1:15">
       <c r="A27" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B27" s="7" t="s">
         <v>37</v>
@@ -2813,7 +2793,7 @@
       </c>
       <c r="D27" s="8"/>
       <c r="F27" s="7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G27" s="7" t="s">
         <v>19</v>
@@ -2845,18 +2825,18 @@
     </row>
     <row r="28" ht="31" spans="1:15">
       <c r="A28" s="12" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B28" s="7" t="s">
         <v>37</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D28" s="8"/>
       <c r="E28" s="7"/>
       <c r="F28" s="7" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G28" s="7" t="s">
         <v>19</v>
@@ -2888,18 +2868,18 @@
     </row>
     <row r="29" spans="1:15">
       <c r="A29" s="12" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>51</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D29" s="8"/>
       <c r="E29" s="7"/>
       <c r="F29" s="7" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G29" s="7" t="s">
         <v>19</v>
@@ -2931,7 +2911,7 @@
     </row>
     <row r="30" spans="1:15">
       <c r="A30" s="12" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B30" s="7" t="s">
         <v>37</v>
@@ -2974,10 +2954,10 @@
     </row>
     <row r="31" ht="31" spans="1:15">
       <c r="A31" s="12" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C31" s="7" t="s">
         <v>33</v>
@@ -2985,7 +2965,7 @@
       <c r="D31" s="8"/>
       <c r="E31" s="7"/>
       <c r="F31" s="7" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G31" s="7" t="s">
         <v>19</v>
@@ -3017,7 +2997,7 @@
     </row>
     <row r="32" spans="1:15">
       <c r="A32" s="12" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B32" s="7" t="s">
         <v>37</v>
@@ -3028,7 +3008,7 @@
       <c r="D32" s="8"/>
       <c r="E32" s="7"/>
       <c r="F32" s="7" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G32" s="7" t="s">
         <v>19</v>
@@ -3060,7 +3040,7 @@
     </row>
     <row r="33" spans="1:15">
       <c r="A33" s="12" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B33" s="7" t="s">
         <v>37</v>
@@ -3071,7 +3051,7 @@
       <c r="D33" s="8"/>
       <c r="E33" s="7"/>
       <c r="F33" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G33" s="7" t="s">
         <v>19</v>
@@ -3103,7 +3083,7 @@
     </row>
     <row r="34" spans="1:15">
       <c r="A34" s="12" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B34" s="7" t="s">
         <v>37</v>
@@ -3114,7 +3094,7 @@
       <c r="D34" s="8"/>
       <c r="E34" s="7"/>
       <c r="F34" s="7" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G34" s="7" t="s">
         <v>19</v>
@@ -3146,7 +3126,7 @@
     </row>
     <row r="35" ht="31" spans="1:15">
       <c r="A35" s="12" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>32</v>
@@ -3157,10 +3137,10 @@
       <c r="D35" s="8"/>
       <c r="E35" s="7"/>
       <c r="F35" s="7" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H35" s="7" t="s">
         <v>19</v>
@@ -3189,21 +3169,21 @@
     </row>
     <row r="36" spans="1:15">
       <c r="A36" s="12" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B36" s="7" t="s">
         <v>32</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D36" s="8"/>
       <c r="E36" s="7"/>
       <c r="F36" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H36" s="7" t="s">
         <v>19</v>
@@ -3232,18 +3212,18 @@
     </row>
     <row r="37" spans="1:15">
       <c r="A37" s="12" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B37" s="7" t="s">
         <v>32</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D37" s="8"/>
       <c r="E37" s="7"/>
       <c r="F37" s="7" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G37" s="7" t="s">
         <v>19</v>
@@ -3275,18 +3255,18 @@
     </row>
     <row r="38" spans="1:15">
       <c r="A38" s="12" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B38" s="7" t="s">
         <v>32</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D38" s="8"/>
       <c r="E38" s="7"/>
       <c r="F38" s="7" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G38" s="7" t="s">
         <v>19</v>
@@ -3318,7 +3298,7 @@
     </row>
     <row r="39" spans="1:15">
       <c r="A39" s="12" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B39" s="7" t="s">
         <v>51</v>
@@ -3329,7 +3309,7 @@
       <c r="D39" s="8"/>
       <c r="E39" s="7"/>
       <c r="F39" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G39" s="7" t="s">
         <v>19</v>
@@ -3361,7 +3341,7 @@
     </row>
     <row r="40" ht="137" spans="1:15">
       <c r="A40" s="12" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B40" s="7" t="s">
         <v>32</v>
@@ -3371,7 +3351,7 @@
       </c>
       <c r="D40" s="8"/>
       <c r="E40" s="7" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F40" s="7" t="s">
         <v>19</v>
@@ -3406,18 +3386,18 @@
     </row>
     <row r="41" ht="31" spans="1:15">
       <c r="A41" s="12" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B41" s="7" t="s">
         <v>32</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D41" s="8"/>
       <c r="E41" s="7"/>
       <c r="F41" s="7" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H41" s="7" t="s">
         <v>19</v>
@@ -3446,20 +3426,20 @@
     </row>
     <row r="42" ht="31" spans="1:15">
       <c r="A42" s="12" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B42" s="7" t="s">
         <v>32</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D42" s="8" t="s">
         <v>19</v>
       </c>
       <c r="E42" s="7"/>
       <c r="F42" s="7" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G42" s="7" t="s">
         <v>19</v>
@@ -3491,10 +3471,10 @@
     </row>
     <row r="43" spans="1:15">
       <c r="A43" s="12" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C43" s="7" t="s">
         <v>33</v>
@@ -3504,7 +3484,7 @@
       </c>
       <c r="E43" s="7"/>
       <c r="F43" s="7" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G43" s="7" t="s">
         <v>19</v>
@@ -3536,23 +3516,23 @@
     </row>
     <row r="44" spans="1:15">
       <c r="A44" s="12" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B44" s="7" t="s">
         <v>32</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D44" s="8" t="s">
         <v>19</v>
       </c>
       <c r="E44" s="7"/>
       <c r="F44" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G44" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H44" s="7" t="s">
         <v>19</v>
@@ -3581,7 +3561,7 @@
     </row>
     <row r="45" spans="1:15">
       <c r="A45" s="12" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B45" s="7" t="s">
         <v>51</v>
@@ -3594,7 +3574,7 @@
       </c>
       <c r="E45" s="7"/>
       <c r="F45" s="7" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G45" s="7" t="s">
         <v>19</v>
@@ -3626,7 +3606,7 @@
     </row>
     <row r="46" spans="1:15">
       <c r="A46" s="12" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>37</v>
@@ -3639,7 +3619,7 @@
       </c>
       <c r="E46" s="7"/>
       <c r="F46" s="7" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G46" s="7" t="s">
         <v>19</v>
@@ -3671,7 +3651,7 @@
     </row>
     <row r="47" spans="1:15">
       <c r="A47" s="12" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B47" s="7" t="s">
         <v>37</v>
@@ -3684,7 +3664,7 @@
       </c>
       <c r="E47" s="7"/>
       <c r="F47" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G47" s="7" t="s">
         <v>19</v>
@@ -3716,10 +3696,10 @@
     </row>
     <row r="48" spans="1:15">
       <c r="A48" s="12" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C48" s="7" t="s">
         <v>33</v>
@@ -3729,7 +3709,7 @@
       </c>
       <c r="E48" s="7"/>
       <c r="F48" s="7" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G48" s="7" t="s">
         <v>19</v>
@@ -3761,7 +3741,7 @@
     </row>
     <row r="49" spans="1:15">
       <c r="A49" s="12" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B49" s="7" t="s">
         <v>67</v>
@@ -3774,7 +3754,7 @@
       </c>
       <c r="E49" s="7"/>
       <c r="F49" s="7" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G49" s="7" t="s">
         <v>19</v>
@@ -3806,7 +3786,7 @@
     </row>
     <row r="50" spans="1:15">
       <c r="A50" s="12" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B50" s="7" t="s">
         <v>32</v>
@@ -3819,7 +3799,7 @@
       </c>
       <c r="E50" s="7"/>
       <c r="F50" s="7" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G50" s="7" t="s">
         <v>19</v>
@@ -3851,7 +3831,7 @@
     </row>
     <row r="51" spans="1:15">
       <c r="A51" s="12" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B51" s="7" t="s">
         <v>67</v>
@@ -3864,7 +3844,7 @@
       </c>
       <c r="E51" s="7"/>
       <c r="F51" s="7" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G51" s="7" t="s">
         <v>19</v>
@@ -3896,7 +3876,7 @@
     </row>
     <row r="52" spans="1:15">
       <c r="A52" s="12" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B52" s="7" t="s">
         <v>67</v>
@@ -3909,7 +3889,7 @@
       </c>
       <c r="E52" s="7"/>
       <c r="F52" s="7" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G52" s="7" t="s">
         <v>19</v>
@@ -3941,10 +3921,10 @@
     </row>
     <row r="53" spans="1:15">
       <c r="A53" s="12" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C53" s="7" t="s">
         <v>33</v>
@@ -3954,7 +3934,7 @@
       </c>
       <c r="E53" s="7"/>
       <c r="F53" s="7" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G53" s="7" t="s">
         <v>19</v>
@@ -3986,7 +3966,7 @@
     </row>
     <row r="54" ht="244" spans="1:15">
       <c r="A54" s="12" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B54" s="7" t="s">
         <v>32</v>
@@ -3998,10 +3978,10 @@
         <v>19</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G54" s="7"/>
       <c r="H54" s="13"/>
@@ -4027,20 +4007,20 @@
     </row>
     <row r="55" spans="1:15">
       <c r="A55" s="12" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B55" s="7" t="s">
         <v>67</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D55" s="8" t="s">
         <v>19</v>
       </c>
       <c r="E55" s="7"/>
       <c r="F55" s="7" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G55" s="7"/>
       <c r="H55" s="7"/>
@@ -4066,20 +4046,20 @@
     </row>
     <row r="56" spans="1:15">
       <c r="A56" s="12" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B56" s="7" t="s">
         <v>51</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D56" s="8" t="s">
         <v>19</v>
       </c>
       <c r="E56" s="7"/>
       <c r="F56" s="7" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G56" s="7"/>
       <c r="H56" s="7"/>
@@ -4105,20 +4085,20 @@
     </row>
     <row r="57" ht="92" spans="1:15">
       <c r="A57" s="12" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>51</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D57" s="8" t="s">
         <v>19</v>
       </c>
       <c r="E57" s="7"/>
       <c r="F57" s="7" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G57" s="7"/>
       <c r="H57" s="7"/>
@@ -4144,20 +4124,20 @@
     </row>
     <row r="58" spans="1:15">
       <c r="A58" s="12" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B58" s="7" t="s">
         <v>32</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D58" s="8" t="s">
         <v>19</v>
       </c>
       <c r="E58" s="7"/>
       <c r="F58" s="7" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G58" s="7" t="s">
         <v>19</v>
@@ -4189,20 +4169,20 @@
     </row>
     <row r="59" spans="1:15">
       <c r="A59" s="12" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B59" s="7" t="s">
         <v>51</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D59" s="8" t="s">
         <v>19</v>
       </c>
       <c r="E59" s="7"/>
       <c r="F59" s="7" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G59" s="7" t="s">
         <v>19</v>
@@ -4234,7 +4214,7 @@
     </row>
     <row r="60" spans="1:15">
       <c r="A60" s="12" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B60" s="7" t="s">
         <v>37</v>
@@ -4247,7 +4227,7 @@
       </c>
       <c r="E60" s="7"/>
       <c r="F60" s="7" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G60" s="7" t="s">
         <v>19</v>
